--- a/components.xlsx
+++ b/components.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30430"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30527"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\queen\Desktop\bc_github\Hruskova_BC\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Queen\Desktop\github\bakalarka\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{B311A34D-5298-48FA-920E-0A041CB5C794}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7BB801E2-0253-4785-927C-A1485E817314}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="22536" windowHeight="13176" xr2:uid="{A7040A42-2CD6-4398-A1C0-C515662F6468}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="51840" windowHeight="21120" xr2:uid="{A7040A42-2CD6-4398-A1C0-C515662F6468}"/>
   </bookViews>
   <sheets>
     <sheet name="List1" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="48" uniqueCount="38">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="146" uniqueCount="94">
   <si>
     <t>PCM5102A sheet</t>
   </si>
@@ -111,9 +111,6 @@
     <t>výstupní RC filtr</t>
   </si>
   <si>
-    <t>mezi CAPP, CAPM, náojová pumpa</t>
-  </si>
-  <si>
     <t>nábojová pumpa u VNEG</t>
   </si>
   <si>
@@ -139,13 +136,184 @@
   </si>
   <si>
     <t>C0G/NP0 +- 5% --&gt; níké zkreslení a stabilní fc</t>
+  </si>
+  <si>
+    <t>stene jako C25</t>
+  </si>
+  <si>
+    <t>Yageo CC0805KRX7R9BB104</t>
+  </si>
+  <si>
+    <t xml:space="preserve">100n, 50V, X7R, </t>
+  </si>
+  <si>
+    <t>vf filtr, avdd</t>
+  </si>
+  <si>
+    <t>avdd zásobní c</t>
+  </si>
+  <si>
+    <t>CPVDD - vf blok</t>
+  </si>
+  <si>
+    <t>CPVDD - zásobní c</t>
+  </si>
+  <si>
+    <t>DVDD - vf blok</t>
+  </si>
+  <si>
+    <t>DVDD - zásobní c</t>
+  </si>
+  <si>
+    <t>LDOO zásobní c</t>
+  </si>
+  <si>
+    <t>C33</t>
+  </si>
+  <si>
+    <t>LDOO - vf blok</t>
+  </si>
+  <si>
+    <t>PCM5102A</t>
+  </si>
+  <si>
+    <t>470R</t>
+  </si>
+  <si>
+    <t>0,1u</t>
+  </si>
+  <si>
+    <t>Murata GCJ31CR71C106KA15L</t>
+  </si>
+  <si>
+    <t>Capacitor_SMD:C_1206_3216Metric</t>
+  </si>
+  <si>
+    <t>16Vm X7R, 1206 - lepší rezerva vůči poklesu c</t>
+  </si>
+  <si>
+    <t>co nejblíže DAC</t>
+  </si>
+  <si>
+    <t>S C24 tvoří LPF 1. řádu</t>
+  </si>
+  <si>
+    <t>S C25 tvoří LPF 1. řádu</t>
+  </si>
+  <si>
+    <t>Resistor_SMD:R_0805_2012Metric</t>
+  </si>
+  <si>
+    <t>UNI-ROYAL 0805W8F4700T5E</t>
+  </si>
+  <si>
+    <t>470 Ohm +-1%, 0805 výkonově stačí</t>
+  </si>
+  <si>
+    <t>mezi CAPP, CAPM, nábojová pumpa</t>
+  </si>
+  <si>
+    <t>blízko LDOO</t>
+  </si>
+  <si>
+    <t>ověřit C_eff při ~1,8V, požadavky LDO</t>
+  </si>
+  <si>
+    <t>co nejblíže pinu AVDD, krátce do gnd</t>
+  </si>
+  <si>
+    <t>TSSOP-20, pitch 0,65mm, pouzdro APWR</t>
+  </si>
+  <si>
+    <t>100 nF, 50V, X7R</t>
+  </si>
+  <si>
+    <t>100 nF, 16V, X7R</t>
+  </si>
+  <si>
+    <t>Headphone Amp sheet</t>
+  </si>
+  <si>
+    <t>C37</t>
+  </si>
+  <si>
+    <t>C40</t>
+  </si>
+  <si>
+    <t>C34</t>
+  </si>
+  <si>
+    <t>C17</t>
+  </si>
+  <si>
+    <t>C18</t>
+  </si>
+  <si>
+    <t>C38</t>
+  </si>
+  <si>
+    <t>R24</t>
+  </si>
+  <si>
+    <t>R25</t>
+  </si>
+  <si>
+    <t>R26</t>
+  </si>
+  <si>
+    <t>R27</t>
+  </si>
+  <si>
+    <t>C39</t>
+  </si>
+  <si>
+    <t>https://www.ti.com/lit/gpn/PCM5102A</t>
+  </si>
+  <si>
+    <t>https://product.samsungsem.com/mlcc/CL21B225KOFNNN.do</t>
+  </si>
+  <si>
+    <t>POWER sheet</t>
+  </si>
+  <si>
+    <t>R1</t>
+  </si>
+  <si>
+    <t>R14</t>
+  </si>
+  <si>
+    <t>R15</t>
+  </si>
+  <si>
+    <t>470u</t>
+  </si>
+  <si>
+    <t>polarizovaný, výstupní vazební L</t>
+  </si>
+  <si>
+    <t>polarizovaný, výstupní vazební R</t>
+  </si>
+  <si>
+    <t>Capacitor_SMD:CP_Elec_6.3x7.7</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6,3V, +-20%, </t>
+  </si>
+  <si>
+    <t>bypass, stabilizace interního VDD/2</t>
+  </si>
+  <si>
+    <t>1u</t>
+  </si>
+  <si>
+    <t>blízko pinu bypass</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="5" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -161,8 +329,31 @@
       <charset val="238"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color theme="10"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <charset val="238"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="Carlito"/>
+      <family val="2"/>
+      <charset val="238"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF175CD3"/>
+      <name val="Carlito"/>
+      <family val="2"/>
+      <charset val="238"/>
+    </font>
   </fonts>
-  <fills count="3">
+  <fills count="4">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -175,6 +366,12 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF5F9FC"/>
+        <bgColor rgb="FF000000"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="1">
     <border>
@@ -185,14 +382,29 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="2">
+    <cellStyle name="Hypertextový odkaz" xfId="1" builtinId="8"/>
     <cellStyle name="Normální" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
@@ -209,9 +421,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Motiv Office">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Motiv Office 2013–2022">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2013 –⁠ 2022">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -249,7 +461,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2013 –⁠ 2022">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -355,7 +567,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2013 –⁠ 2022">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -497,32 +709,57 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
 </file>
 
+<file path=xl/webextensions/taskpanes.xml><?xml version="1.0" encoding="utf-8"?>
+<wetp:taskpanes xmlns:wetp="http://schemas.microsoft.com/office/webextensions/taskpanes/2010/11">
+  <wetp:taskpane dockstate="right" visibility="0" width="350" row="1">
+    <wetp:webextensionref xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+  </wetp:taskpane>
+</wetp:taskpanes>
+</file>
+
+<file path=xl/webextensions/webextension1.xml><?xml version="1.0" encoding="utf-8"?>
+<we:webextension xmlns:we="http://schemas.microsoft.com/office/webextensions/webextension/2010/11" id="{646367AC-4870-4159-A7D1-FDA884F15A11}">
+  <we:reference id="29673e3c-d826-4f00-92ee-162334a52b1a" version="1.0.0.8" store="EXCatalog" storeType="EXCatalog"/>
+  <we:alternateReferences>
+    <we:reference id="WA200009404" version="1.0.0.8" store="cs-CZ" storeType="OMEX"/>
+  </we:alternateReferences>
+  <we:properties>
+    <we:property name="claude.fileId" value="&quot;dc3f2ce2-46f2-419d-b2fc-503f4fae3e49&quot;"/>
+  </we:properties>
+  <we:bindings/>
+  <we:snapshot xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships"/>
+</we:webextension>
+</file>
+
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F083952E-014D-4852-9059-7FD571C71C39}">
-  <dimension ref="A3:H18"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <dimension ref="A3:J50"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="2" max="2" width="50.5546875" customWidth="1"/>
-    <col min="4" max="4" width="31.33203125" customWidth="1"/>
-    <col min="5" max="5" width="26.109375" customWidth="1"/>
+    <col min="2" max="2" width="50.5703125" customWidth="1"/>
+    <col min="3" max="3" width="11.85546875" customWidth="1"/>
+    <col min="4" max="4" width="37.5703125" customWidth="1"/>
+    <col min="5" max="5" width="40.85546875" customWidth="1"/>
     <col min="6" max="6" width="18" customWidth="1"/>
-    <col min="7" max="7" width="36.21875" customWidth="1"/>
+    <col min="7" max="7" width="41.5703125" customWidth="1"/>
     <col min="8" max="8" width="24" customWidth="1"/>
+    <col min="9" max="9" width="11.28515625" customWidth="1"/>
+    <col min="10" max="10" width="64.42578125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
         <v>0</v>
       </c>
       <c r="B3" s="1"/>
     </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:10" x14ac:dyDescent="0.25">
       <c r="C4" t="s">
         <v>12</v>
       </c>
@@ -536,15 +773,15 @@
         <v>19</v>
       </c>
       <c r="G4" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.3">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="5" spans="1:10" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>1</v>
       </c>
       <c r="B5" t="s">
-        <v>28</v>
+        <v>61</v>
       </c>
       <c r="C5" t="s">
         <v>13</v>
@@ -559,18 +796,21 @@
         <v>18</v>
       </c>
       <c r="G5" t="s">
+        <v>30</v>
+      </c>
+      <c r="H5" t="s">
         <v>31</v>
       </c>
-      <c r="H5" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="J5" s="6" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="6" spans="1:10" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>2</v>
       </c>
       <c r="B6" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="C6" t="s">
         <v>13</v>
@@ -582,21 +822,24 @@
         <v>17</v>
       </c>
       <c r="G6" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="H6" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="7" spans="1:8" x14ac:dyDescent="0.3">
+        <v>31</v>
+      </c>
+      <c r="J6" s="5" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="7" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>3</v>
       </c>
       <c r="B7" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C7" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="D7" t="s">
         <v>15</v>
@@ -604,16 +847,19 @@
       <c r="E7" t="s">
         <v>17</v>
       </c>
-    </row>
-    <row r="8" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="G7" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="8" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>4</v>
       </c>
       <c r="B8" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C8" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="D8" t="s">
         <v>15</v>
@@ -625,82 +871,405 @@
         <v>37</v>
       </c>
     </row>
-    <row r="9" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>5</v>
       </c>
+      <c r="B9" t="s">
+        <v>40</v>
+      </c>
       <c r="C9" t="s">
         <v>25</v>
       </c>
-    </row>
-    <row r="10" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="D9" t="s">
+        <v>15</v>
+      </c>
+      <c r="E9" t="s">
+        <v>38</v>
+      </c>
+      <c r="G9" t="s">
+        <v>39</v>
+      </c>
+      <c r="H9" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="10" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>6</v>
       </c>
+      <c r="B10" t="s">
+        <v>41</v>
+      </c>
       <c r="C10" t="s">
         <v>26</v>
       </c>
-    </row>
-    <row r="11" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="D10" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="E10" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="G10" t="s">
+        <v>54</v>
+      </c>
+      <c r="H10" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="11" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="12" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="B11" t="s">
+        <v>42</v>
+      </c>
+      <c r="C11" t="s">
+        <v>51</v>
+      </c>
+      <c r="D11" t="s">
+        <v>15</v>
+      </c>
+      <c r="E11" t="s">
+        <v>38</v>
+      </c>
+      <c r="G11" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="12" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="13" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="B12" t="s">
+        <v>43</v>
+      </c>
+      <c r="C12" t="s">
+        <v>26</v>
+      </c>
+      <c r="D12" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="E12" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="G12" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="13" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>9</v>
       </c>
-    </row>
-    <row r="14" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="B13" t="s">
+        <v>44</v>
+      </c>
+      <c r="C13" t="s">
+        <v>51</v>
+      </c>
+      <c r="D13" t="s">
+        <v>15</v>
+      </c>
+      <c r="E13" t="s">
+        <v>38</v>
+      </c>
+      <c r="G13" t="s">
+        <v>66</v>
+      </c>
+      <c r="H13" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="14" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="15" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="B14" t="s">
+        <v>45</v>
+      </c>
+      <c r="C14" t="s">
+        <v>26</v>
+      </c>
+      <c r="D14" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="E14" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="G14" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="15" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="16" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="B15" t="s">
+        <v>46</v>
+      </c>
+      <c r="C15" t="s">
+        <v>26</v>
+      </c>
+      <c r="D15" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="E15" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="G15" t="s">
+        <v>67</v>
+      </c>
+      <c r="H15" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="16" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
+        <v>47</v>
+      </c>
+      <c r="B16" t="s">
+        <v>48</v>
+      </c>
+      <c r="C16" t="s">
+        <v>51</v>
+      </c>
+      <c r="D16" t="s">
+        <v>15</v>
+      </c>
+      <c r="E16" t="s">
+        <v>38</v>
+      </c>
+      <c r="G16" t="s">
+        <v>66</v>
+      </c>
+      <c r="H16" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="17" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A17" t="s">
         <v>20</v>
-      </c>
-      <c r="B16" t="s">
-        <v>27</v>
-      </c>
-      <c r="C16">
-        <v>470</v>
-      </c>
-    </row>
-    <row r="17" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A17" t="s">
-        <v>21</v>
       </c>
       <c r="B17" t="s">
         <v>27</v>
       </c>
-      <c r="C17">
-        <v>470</v>
-      </c>
-    </row>
-    <row r="18" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="C17" t="s">
+        <v>50</v>
+      </c>
+      <c r="D17" s="3" t="s">
+        <v>58</v>
+      </c>
+      <c r="E17" t="s">
+        <v>59</v>
+      </c>
+      <c r="G17" t="s">
+        <v>60</v>
+      </c>
+      <c r="H17" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="18" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
+        <v>21</v>
+      </c>
+      <c r="B18" t="s">
+        <v>27</v>
+      </c>
+      <c r="C18" t="s">
+        <v>50</v>
+      </c>
+      <c r="D18" s="3" t="s">
+        <v>58</v>
+      </c>
+      <c r="E18" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="G18" t="s">
+        <v>60</v>
+      </c>
+      <c r="H18" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="19" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A19" t="s">
         <v>22</v>
       </c>
-      <c r="B18" t="s">
+      <c r="B19" t="s">
         <v>23</v>
       </c>
-      <c r="E18" t="s">
+      <c r="C19" t="s">
+        <v>49</v>
+      </c>
+      <c r="E19" t="s">
         <v>24</v>
+      </c>
+      <c r="G19" t="s">
+        <v>65</v>
+      </c>
+      <c r="J19" s="4" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="22" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A22" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="B22" s="1"/>
+    </row>
+    <row r="23" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="C23" t="s">
+        <v>12</v>
+      </c>
+      <c r="D23" t="s">
+        <v>14</v>
+      </c>
+      <c r="E23" t="s">
+        <v>16</v>
+      </c>
+      <c r="F23" t="s">
+        <v>19</v>
+      </c>
+      <c r="G23" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="24" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A24" t="s">
+        <v>72</v>
+      </c>
+      <c r="B24" t="s">
+        <v>88</v>
+      </c>
+      <c r="C24" t="s">
+        <v>86</v>
+      </c>
+      <c r="D24" t="s">
+        <v>89</v>
+      </c>
+      <c r="G24" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="25" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A25" t="s">
+        <v>73</v>
+      </c>
+      <c r="B25" t="s">
+        <v>87</v>
+      </c>
+      <c r="C25" t="s">
+        <v>86</v>
+      </c>
+      <c r="D25" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="26" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A26" t="s">
+        <v>71</v>
+      </c>
+      <c r="B26" t="s">
+        <v>91</v>
+      </c>
+      <c r="C26" t="s">
+        <v>92</v>
+      </c>
+      <c r="D26" t="s">
+        <v>15</v>
+      </c>
+      <c r="E26" t="s">
+        <v>17</v>
+      </c>
+      <c r="H26" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="27" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A27" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="28" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A28" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="29" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A29" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="30" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A30" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="31" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A31" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="32" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A32" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="33" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A33" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="34" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A34" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="39" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A39" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="B39" s="1"/>
+    </row>
+    <row r="40" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="C40" t="s">
+        <v>12</v>
+      </c>
+      <c r="D40" t="s">
+        <v>14</v>
+      </c>
+      <c r="E40" t="s">
+        <v>16</v>
+      </c>
+      <c r="F40" t="s">
+        <v>19</v>
+      </c>
+      <c r="G40" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="41" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A41" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="49" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A49" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="50" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A50" t="s">
+        <v>85</v>
       </c>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
+  <hyperlinks>
+    <hyperlink ref="J19" r:id="rId1" xr:uid="{98DC3493-B69F-436B-8BDA-88FF0BD1F929}"/>
+    <hyperlink ref="J5" r:id="rId2" xr:uid="{4566AD17-299C-4222-B460-9D159B2114C6}"/>
+  </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.78740157499999996" bottom="0.78740157499999996" header="0.3" footer="0.3"/>
 </worksheet>
 </file>